--- a/AAII_Financials/Quarterly/AKAN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AKAN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="92">
   <si>
     <t>AKAN</t>
   </si>
@@ -656,46 +656,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="E7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="F7" s="2">
+        <v>44742</v>
+      </c>
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>44469</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I7" s="2" t="s">
         <v>3</v>
       </c>
@@ -705,51 +708,69 @@
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>1400</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="F8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
+        <v>600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>600</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -763,22 +784,31 @@
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>100</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -792,8 +822,17 @@
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -805,8 +844,11 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -834,8 +876,17 @@
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -863,22 +914,31 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>700</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -892,22 +952,31 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>300</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
+        <v>2200</v>
+      </c>
+      <c r="E15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>3</v>
@@ -921,8 +990,17 @@
       <c r="K15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -931,26 +1009,29 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>6800</v>
+        <v>7200</v>
       </c>
       <c r="E17" s="3">
+        <v>22700</v>
+      </c>
+      <c r="F17" s="3">
+        <v>11000</v>
+      </c>
+      <c r="G17" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H17" s="3">
         <v>100</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I17" s="3" t="s">
         <v>3</v>
       </c>
@@ -960,22 +1041,31 @@
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-5800</v>
       </c>
       <c r="E18" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
+        <v>-20100</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-2500</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
@@ -989,8 +1079,17 @@
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1002,22 +1101,25 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
+        <v>11900</v>
+      </c>
+      <c r="F20" s="3">
+        <v>12000</v>
+      </c>
+      <c r="G20" s="3">
+        <v>100</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
@@ -1031,19 +1133,28 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="F21" s="3">
+        <v>2800</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>3</v>
@@ -1060,8 +1171,17 @@
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1089,26 +1209,35 @@
       <c r="K22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-8000</v>
+        <v>-5900</v>
       </c>
       <c r="E23" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="H23" s="3">
         <v>-100</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1118,8 +1247,17 @@
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1147,8 +1285,17 @@
       <c r="K24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1176,26 +1323,35 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-8000</v>
+        <v>-5900</v>
       </c>
       <c r="E26" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="F26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="H26" s="3">
         <v>-100</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1205,26 +1361,35 @@
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-8000</v>
+        <v>-5900</v>
       </c>
       <c r="E27" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="F27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="H27" s="3">
         <v>-100</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1234,8 +1399,17 @@
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1263,8 +1437,17 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1272,28 +1455,37 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>-3400</v>
       </c>
       <c r="F29" s="3">
-        <v>0</v>
+        <v>-3700</v>
       </c>
       <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+        <v>-5700</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1321,8 +1513,17 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1350,22 +1551,31 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>100</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
+        <v>-11900</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-100</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
@@ -1379,26 +1589,35 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="G33" s="3">
         <v>-8000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="H33" s="3">
         <v>-100</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1408,8 +1627,17 @@
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1437,26 +1665,35 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="G35" s="3">
         <v>-8000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="H35" s="3">
         <v>-100</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1466,31 +1703,40 @@
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="E38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="F38" s="2">
+        <v>44742</v>
+      </c>
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>44469</v>
       </c>
-      <c r="F38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1500,8 +1746,17 @@
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1513,8 +1768,11 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1526,142 +1784,181 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F41" s="3">
-        <v>0</v>
-      </c>
-      <c r="G41" s="3">
-        <v>0</v>
-      </c>
-      <c r="H41" s="3">
-        <v>0</v>
-      </c>
-      <c r="I41" s="3">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3">
-        <v>0</v>
+        <v>3900</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3">
+        <v>0</v>
+      </c>
+      <c r="M41" s="3">
+        <v>0</v>
+      </c>
+      <c r="N41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+        <v>700</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+        <v>900</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G45" s="3">
         <v>4000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1671,26 +1968,35 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F46" s="3">
+        <v>6900</v>
+      </c>
+      <c r="G46" s="3">
         <v>4000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="H46" s="3">
         <v>300</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1700,52 +2006,70 @@
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>12500</v>
+      </c>
+      <c r="F48" s="3">
+        <v>12600</v>
+      </c>
+      <c r="G48" s="3">
         <v>3800</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1758,23 +2082,32 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>22200</v>
+      </c>
+      <c r="F49" s="3">
+        <v>23400</v>
+      </c>
+      <c r="G49" s="3">
         <v>300</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
       </c>
@@ -1787,8 +2120,17 @@
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1816,8 +2158,17 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1845,8 +2196,17 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -1874,8 +2234,17 @@
       <c r="K52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1903,26 +2272,35 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>36500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>39000</v>
+      </c>
+      <c r="F54" s="3">
+        <v>43500</v>
+      </c>
+      <c r="G54" s="3">
         <v>8000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="H54" s="3">
         <v>300</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
       </c>
@@ -1932,8 +2310,17 @@
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1945,8 +2332,11 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1958,26 +2348,29 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F57" s="3">
+        <v>4500</v>
+      </c>
+      <c r="G57" s="3">
         <v>700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="H57" s="3">
         <v>100</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
       </c>
@@ -1987,25 +2380,34 @@
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G58" s="3">
         <v>7600</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
+      <c r="H58" s="3">
+        <v>0</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
@@ -2016,55 +2418,73 @@
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E59" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3">
+        <v>0</v>
+      </c>
+      <c r="M59" s="3">
+        <v>0</v>
+      </c>
+      <c r="N59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F60" s="3">
+        <v>6300</v>
+      </c>
+      <c r="G60" s="3">
         <v>8300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="H60" s="3">
         <v>100</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2074,23 +2494,32 @@
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F61" s="3">
+        <v>2600</v>
+      </c>
+      <c r="G61" s="3">
         <v>2000</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
@@ -2103,8 +2532,17 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2132,8 +2570,17 @@
       <c r="K62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2161,8 +2608,17 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2190,8 +2646,17 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2219,26 +2684,35 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>12100</v>
+      </c>
+      <c r="F66" s="3">
+        <v>8800</v>
+      </c>
+      <c r="G66" s="3">
         <v>10200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="H66" s="3">
         <v>100</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2248,8 +2722,17 @@
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2261,8 +2744,11 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2290,8 +2776,17 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2319,8 +2814,17 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2348,8 +2852,17 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2377,26 +2890,35 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-21100</v>
+      </c>
+      <c r="F72" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="G72" s="3">
         <v>-13300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="H72" s="3">
         <v>-100</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2406,8 +2928,17 @@
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2435,8 +2966,17 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2464,8 +3004,17 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2493,26 +3042,35 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>26900</v>
+      </c>
+      <c r="F76" s="3">
+        <v>34600</v>
+      </c>
+      <c r="G76" s="3">
         <v>-2200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="H76" s="3">
         <v>200</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2522,8 +3080,17 @@
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2551,31 +3118,40 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="E80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="F80" s="2">
+        <v>44742</v>
+      </c>
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>44469</v>
       </c>
-      <c r="F80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2585,26 +3161,35 @@
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="G81" s="3">
         <v>-8000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="H81" s="3">
         <v>-100</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I81" s="3" t="s">
         <v>3</v>
       </c>
@@ -2614,8 +3199,17 @@
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2627,37 +3221,49 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+        <v>1700</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2685,8 +3291,17 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2714,8 +3329,17 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2743,8 +3367,17 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2772,8 +3405,17 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2801,25 +3443,34 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="F89" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="G89" s="3">
         <v>-6500</v>
       </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
+      <c r="H89" s="3">
+        <v>0</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>3</v>
@@ -2830,8 +3481,17 @@
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2843,8 +3503,11 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -2855,7 +3518,7 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-1100</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -2872,8 +3535,17 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2901,8 +3573,17 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2930,8 +3611,17 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -2939,28 +3629,37 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>-4200</v>
       </c>
       <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+        <v>-4200</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2972,8 +3671,11 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3001,8 +3703,17 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3030,8 +3741,17 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3059,8 +3779,17 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3088,26 +3817,35 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>14100</v>
+      </c>
+      <c r="F100" s="3">
+        <v>14600</v>
+      </c>
+      <c r="G100" s="3">
         <v>11000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="H100" s="3">
         <v>300</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3117,25 +3855,34 @@
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="G101" s="3">
         <v>-600</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
+      <c r="H101" s="3">
+        <v>0</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
@@ -3146,26 +3893,35 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F102" s="3">
+        <v>900</v>
+      </c>
+      <c r="G102" s="3">
         <v>3200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="H102" s="3">
         <v>300</v>
       </c>
-      <c r="F102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I102" s="3" t="s">
         <v>3</v>
       </c>
@@ -3173,6 +3929,15 @@
         <v>3</v>
       </c>
       <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AKAN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AKAN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="92">
   <si>
     <t>AKAN</t>
   </si>
@@ -656,52 +656,53 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44469</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
@@ -717,25 +718,28 @@
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E8" s="3">
         <v>1400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>100</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
+      <c r="H8" s="3">
+        <v>0</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
@@ -743,8 +747,8 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -755,25 +759,28 @@
       <c r="N8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>600</v>
+        <v>1900</v>
       </c>
       <c r="E9" s="3">
         <v>600</v>
       </c>
       <c r="F9" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
+      <c r="H9" s="3">
+        <v>0</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
@@ -793,25 +800,28 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>300</v>
+      </c>
+      <c r="E10" s="3">
         <v>800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>100</v>
       </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
+      <c r="H10" s="3">
+        <v>0</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
@@ -831,8 +841,11 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -847,8 +860,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -885,8 +899,11 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -923,25 +940,28 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E14" s="3">
         <v>-100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-1300</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+      <c r="H14" s="3">
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -961,25 +981,28 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E15" s="3">
         <v>2200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1500</v>
       </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
+      <c r="H15" s="3">
+        <v>0</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>3</v>
@@ -999,8 +1022,11 @@
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1012,29 +1038,30 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>36800</v>
+      </c>
+      <c r="E17" s="3">
         <v>7200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>22700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>11000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>100</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1050,26 +1077,29 @@
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-34600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-20100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-10900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2500</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1088,8 +1118,11 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1104,26 +1137,27 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>11900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>12000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1142,23 +1176,26 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-4500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2800</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1180,8 +1217,11 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1218,29 +1258,32 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-32300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-100</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1256,8 +1299,11 @@
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1294,8 +1340,11 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1332,29 +1381,32 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-32300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-8200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-100</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1370,29 +1422,32 @@
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-32300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-8200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-100</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1408,8 +1463,11 @@
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1446,8 +1504,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1455,25 +1516,25 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>-3400</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-3700</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-5700</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I29" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -1484,8 +1545,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1522,8 +1586,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1560,26 +1627,29 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-11900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-12000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1598,29 +1668,32 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-32300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-11700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-100</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1636,8 +1709,11 @@
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1674,29 +1750,32 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-32300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-11700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-100</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1712,34 +1791,37 @@
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44469</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1755,8 +1837,11 @@
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1771,8 +1856,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1787,23 +1873,24 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>100</v>
+      </c>
+      <c r="E41" s="3">
         <v>400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3900</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1813,8 +1900,8 @@
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K41" s="3">
-        <v>0</v>
+      <c r="K41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L41" s="3">
         <v>0</v>
@@ -1825,13 +1912,16 @@
       <c r="N41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
         <v>300</v>
@@ -1839,8 +1929,8 @@
       <c r="F42" s="3">
         <v>300</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
+      <c r="G42" s="3">
+        <v>300</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>3</v>
@@ -1851,8 +1941,8 @@
       <c r="J42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
+      <c r="K42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -1863,23 +1953,26 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>300</v>
+      </c>
+      <c r="E43" s="3">
         <v>700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>700</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1889,8 +1982,8 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -1901,8 +1994,11 @@
       <c r="N43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1910,14 +2006,14 @@
         <v>1300</v>
       </c>
       <c r="E44" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F44" s="3">
         <v>1100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>900</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1927,8 +2023,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -1939,29 +2035,32 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>200</v>
+      </c>
+      <c r="E45" s="3">
         <v>600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1977,29 +2076,32 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E46" s="3">
         <v>3200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>300</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2015,13 +2117,16 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E47" s="3">
         <v>500</v>
@@ -2029,8 +2134,8 @@
       <c r="F47" s="3">
         <v>500</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
+      <c r="G47" s="3">
+        <v>500</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
@@ -2041,8 +2146,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2053,26 +2158,29 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E48" s="3">
         <v>11800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>12600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3800</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2091,26 +2199,29 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E49" s="3">
         <v>21000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>22200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>23400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>300</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2129,8 +2240,11 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2167,8 +2281,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2205,8 +2322,11 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2243,8 +2363,11 @@
       <c r="N52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2281,29 +2404,32 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E54" s="3">
         <v>36500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>39000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>43500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>300</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2319,8 +2445,11 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2335,8 +2464,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2351,29 +2481,30 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E57" s="3">
         <v>8500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>100</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2389,28 +2520,31 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E58" s="3">
         <v>2700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7600</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
+      <c r="I58" s="3">
+        <v>0</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
@@ -2427,23 +2561,26 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E59" s="3">
         <v>1200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>500</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2453,8 +2590,8 @@
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
+      <c r="K59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
@@ -2465,29 +2602,32 @@
       <c r="N59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E60" s="3">
         <v>12400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>100</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2503,8 +2643,11 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2512,17 +2655,17 @@
         <v>2500</v>
       </c>
       <c r="E61" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F61" s="3">
         <v>2700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2000</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2541,8 +2684,11 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2579,8 +2725,11 @@
       <c r="N62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2617,8 +2766,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2655,8 +2807,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2693,29 +2848,32 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E66" s="3">
         <v>14900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>100</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2731,8 +2889,11 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2747,8 +2908,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2785,8 +2947,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2823,8 +2988,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2861,8 +3029,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2899,29 +3070,32 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-53400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-27000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-21100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-12000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-13300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-100</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2937,8 +3111,11 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2975,8 +3152,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3013,8 +3193,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3051,29 +3234,32 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E76" s="3">
         <v>21600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>26900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>34600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-2200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>200</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3089,8 +3275,11 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3127,34 +3316,37 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44469</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3170,29 +3362,32 @@
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-32300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-11700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-100</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3208,8 +3403,11 @@
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3224,23 +3422,24 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E83" s="3">
         <v>2200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1700</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3250,8 +3449,8 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -3262,8 +3461,11 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3300,8 +3502,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3338,8 +3543,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3376,8 +3584,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3414,8 +3625,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3452,28 +3666,31 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-11500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-8400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-6500</v>
       </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
+      <c r="I89" s="3">
+        <v>0</v>
       </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
@@ -3490,8 +3707,11 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3506,8 +3726,9 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3518,11 +3739,11 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-1100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
@@ -3544,8 +3765,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3582,8 +3806,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3620,8 +3847,11 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3629,13 +3859,13 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
-        <v>-4200</v>
+        <v>0</v>
       </c>
       <c r="F94" s="3">
         <v>-4200</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
+      <c r="G94" s="3">
+        <v>-4200</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
@@ -3646,8 +3876,8 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -3658,8 +3888,11 @@
       <c r="N94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3674,8 +3907,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3712,8 +3946,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3750,8 +3987,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3788,8 +4028,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3826,29 +4069,32 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E100" s="3">
         <v>1200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>14100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>14600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>11000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>300</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,28 +4110,31 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-600</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
+      <c r="I101" s="3">
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
@@ -3902,29 +4151,32 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E102" s="3">
         <v>200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>300</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J102" s="3" t="s">
         <v>3</v>
       </c>
@@ -3938,6 +4190,9 @@
         <v>3</v>
       </c>
       <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AKAN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AKAN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="92">
   <si>
     <t>AKAN</t>
   </si>
@@ -656,59 +656,60 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44469</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
@@ -721,40 +722,46 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>2200</v>
+        <v>200</v>
       </c>
       <c r="E8" s="3">
-        <v>1400</v>
+        <v>200</v>
       </c>
       <c r="F8" s="3">
-        <v>2600</v>
+        <v>400</v>
       </c>
       <c r="G8" s="3">
+        <v>400</v>
+      </c>
+      <c r="H8" s="3">
         <v>100</v>
       </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
+      <c r="I8" s="3">
+        <v>100</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1300</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -762,31 +769,37 @@
       <c r="O8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1900</v>
+        <v>200</v>
       </c>
       <c r="E9" s="3">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="F9" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="G9" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="H9" s="3">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="I9" s="3">
+        <v>100</v>
+      </c>
+      <c r="J9" s="3">
+        <v>-300</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -803,31 +816,37 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E10" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="F10" s="3">
-        <v>2000</v>
+        <v>-400</v>
       </c>
       <c r="G10" s="3">
-        <v>100</v>
+        <v>-400</v>
       </c>
       <c r="H10" s="3">
         <v>0</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1600</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -844,8 +863,14 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -861,8 +886,10 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -902,8 +929,14 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -943,31 +976,37 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>24700</v>
+        <v>-100</v>
       </c>
       <c r="E14" s="3">
         <v>-100</v>
       </c>
       <c r="F14" s="3">
-        <v>-1300</v>
+        <v>11200</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>11200</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-100</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -984,31 +1023,37 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>4300</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>2200</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>3600</v>
+        <v>1100</v>
       </c>
       <c r="G15" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="I15" s="3">
+        <v>100</v>
+      </c>
+      <c r="J15" s="3">
+        <v>1000</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
@@ -1025,8 +1070,14 @@
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1039,35 +1090,37 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>36800</v>
+        <v>1400</v>
       </c>
       <c r="E17" s="3">
-        <v>7200</v>
+        <v>1400</v>
       </c>
       <c r="F17" s="3">
-        <v>22700</v>
+        <v>2400</v>
       </c>
       <c r="G17" s="3">
-        <v>11000</v>
+        <v>2400</v>
       </c>
       <c r="H17" s="3">
-        <v>2500</v>
+        <v>1400</v>
       </c>
       <c r="I17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J17" s="3">
+        <v>6000</v>
+      </c>
+      <c r="K17" s="3">
         <v>100</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1080,31 +1133,37 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-34600</v>
+        <v>-1200</v>
       </c>
       <c r="E18" s="3">
-        <v>-5800</v>
+        <v>-1200</v>
       </c>
       <c r="F18" s="3">
-        <v>-20100</v>
+        <v>-2000</v>
       </c>
       <c r="G18" s="3">
-        <v>-10900</v>
+        <v>-2000</v>
       </c>
       <c r="H18" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+        <v>-1300</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-4800</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1121,8 +1180,14 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1138,31 +1203,33 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>11900</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>100</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1179,32 +1246,38 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-28000</v>
+        <v>-1100</v>
       </c>
       <c r="E21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="J21" s="3">
         <v>-3700</v>
       </c>
-      <c r="F21" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="G21" s="3">
-        <v>2800</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1220,8 +1293,14 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1261,35 +1340,41 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-32300</v>
+        <v>-1100</v>
       </c>
       <c r="E23" s="3">
-        <v>-5900</v>
+        <v>-1100</v>
       </c>
       <c r="F23" s="3">
-        <v>-8200</v>
+        <v>-13200</v>
       </c>
       <c r="G23" s="3">
-        <v>1200</v>
+        <v>-13200</v>
       </c>
       <c r="H23" s="3">
-        <v>-2400</v>
+        <v>-1300</v>
       </c>
       <c r="I23" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="K23" s="3">
         <v>-100</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1302,31 +1387,37 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1343,8 +1434,14 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1384,35 +1481,41 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-32300</v>
+        <v>-1100</v>
       </c>
       <c r="E26" s="3">
-        <v>-5900</v>
+        <v>-1100</v>
       </c>
       <c r="F26" s="3">
-        <v>-8200</v>
+        <v>-13200</v>
       </c>
       <c r="G26" s="3">
-        <v>1200</v>
+        <v>-13200</v>
       </c>
       <c r="H26" s="3">
-        <v>-2400</v>
+        <v>-1300</v>
       </c>
       <c r="I26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="K26" s="3">
         <v>-100</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1425,35 +1528,41 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-32300</v>
+        <v>-1300</v>
       </c>
       <c r="E27" s="3">
-        <v>-5900</v>
+        <v>-1300</v>
       </c>
       <c r="F27" s="3">
-        <v>-8200</v>
+        <v>-13200</v>
       </c>
       <c r="G27" s="3">
-        <v>1200</v>
+        <v>-13200</v>
       </c>
       <c r="H27" s="3">
-        <v>-2400</v>
+        <v>-2900</v>
       </c>
       <c r="I27" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="K27" s="3">
         <v>-100</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1466,8 +1575,14 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1507,40 +1622,46 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="F29" s="3">
-        <v>-3400</v>
+        <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>-3700</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
+        <v>-1600</v>
+      </c>
+      <c r="I29" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="J29" s="3">
+        <v>200</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -1548,8 +1669,14 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1589,8 +1716,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1630,31 +1763,37 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2300</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-11900</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-12000</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1671,35 +1810,41 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-32300</v>
+        <v>-1300</v>
       </c>
       <c r="E33" s="3">
-        <v>-5900</v>
+        <v>-1300</v>
       </c>
       <c r="F33" s="3">
-        <v>-11700</v>
+        <v>-13200</v>
       </c>
       <c r="G33" s="3">
-        <v>-2600</v>
+        <v>-13200</v>
       </c>
       <c r="H33" s="3">
-        <v>-8000</v>
+        <v>-2900</v>
       </c>
       <c r="I33" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="K33" s="3">
         <v>-100</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1712,8 +1857,14 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1753,35 +1904,41 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-32300</v>
+        <v>-1300</v>
       </c>
       <c r="E35" s="3">
-        <v>-5900</v>
+        <v>-1300</v>
       </c>
       <c r="F35" s="3">
-        <v>-11700</v>
+        <v>-13200</v>
       </c>
       <c r="G35" s="3">
-        <v>-2600</v>
+        <v>-13200</v>
       </c>
       <c r="H35" s="3">
-        <v>-8000</v>
+        <v>-2900</v>
       </c>
       <c r="I35" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="K35" s="3">
         <v>-100</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1794,40 +1951,46 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44469</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1840,8 +2003,14 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1857,8 +2026,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1874,40 +2045,42 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F41" s="3">
         <v>100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
+        <v>100</v>
+      </c>
+      <c r="H41" s="3">
         <v>400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="I41" s="3">
+        <v>400</v>
+      </c>
+      <c r="J41" s="3">
         <v>200</v>
       </c>
-      <c r="G41" s="3">
-        <v>3900</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L41" s="3">
-        <v>0</v>
-      </c>
-      <c r="M41" s="3">
-        <v>0</v>
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N41" s="3">
         <v>0</v>
@@ -1915,8 +2088,14 @@
       <c r="O41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1924,31 +2103,31 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="I42" s="3">
         <v>300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="J42" s="3">
         <v>300</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
+      <c r="L42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -1956,8 +2135,14 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1965,31 +2150,31 @@
         <v>300</v>
       </c>
       <c r="E43" s="3">
+        <v>300</v>
+      </c>
+      <c r="F43" s="3">
+        <v>300</v>
+      </c>
+      <c r="G43" s="3">
+        <v>300</v>
+      </c>
+      <c r="H43" s="3">
         <v>700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="I43" s="3">
+        <v>700</v>
+      </c>
+      <c r="J43" s="3">
         <v>1200</v>
       </c>
-      <c r="G43" s="3">
-        <v>700</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -1997,40 +2182,46 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3">
         <v>1300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I44" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J44" s="3">
         <v>1100</v>
       </c>
-      <c r="G44" s="3">
-        <v>900</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2038,34 +2229,40 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>200</v>
-      </c>
-      <c r="E45" s="3">
-        <v>600</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>1100</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H45" s="3">
-        <v>4000</v>
+        <v>300</v>
       </c>
       <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
+      <c r="J45" s="3">
+        <v>800</v>
+      </c>
+      <c r="K45" s="3">
+        <v>300</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
@@ -2079,35 +2276,41 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F46" s="3">
         <v>1800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H46" s="3">
         <v>3200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="I46" s="3">
+        <v>3200</v>
+      </c>
+      <c r="J46" s="3">
         <v>3800</v>
       </c>
-      <c r="G46" s="3">
-        <v>6900</v>
-      </c>
-      <c r="H46" s="3">
-        <v>4000</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>300</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2120,22 +2323,28 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>600</v>
-      </c>
-      <c r="E47" s="3">
-        <v>500</v>
-      </c>
-      <c r="F47" s="3">
-        <v>500</v>
-      </c>
-      <c r="G47" s="3">
-        <v>500</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
@@ -2149,11 +2358,11 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2161,32 +2370,38 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F48" s="3">
         <v>2600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H48" s="3">
         <v>11800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="I48" s="3">
+        <v>11800</v>
+      </c>
+      <c r="J48" s="3">
         <v>12500</v>
       </c>
-      <c r="G48" s="3">
-        <v>12600</v>
-      </c>
-      <c r="H48" s="3">
-        <v>3800</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2202,32 +2417,38 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>3800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
+        <v>3800</v>
+      </c>
+      <c r="H49" s="3">
         <v>21000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="I49" s="3">
+        <v>21000</v>
+      </c>
+      <c r="J49" s="3">
         <v>22200</v>
       </c>
-      <c r="G49" s="3">
-        <v>23400</v>
-      </c>
-      <c r="H49" s="3">
-        <v>300</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2243,8 +2464,14 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2284,8 +2511,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2325,31 +2558,37 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2366,8 +2605,14 @@
       <c r="O52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2407,35 +2652,41 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F54" s="3">
         <v>8800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
+        <v>8800</v>
+      </c>
+      <c r="H54" s="3">
         <v>36500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
+        <v>36500</v>
+      </c>
+      <c r="J54" s="3">
         <v>39000</v>
       </c>
-      <c r="G54" s="3">
-        <v>43500</v>
-      </c>
-      <c r="H54" s="3">
-        <v>8000</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>300</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2448,8 +2699,14 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2465,8 +2722,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2482,35 +2741,37 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F57" s="3">
         <v>6000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
+        <v>6000</v>
+      </c>
+      <c r="H57" s="3">
         <v>8500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="I57" s="3">
+        <v>8500</v>
+      </c>
+      <c r="J57" s="3">
         <v>7100</v>
       </c>
-      <c r="G57" s="3">
-        <v>4500</v>
-      </c>
-      <c r="H57" s="3">
-        <v>700</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>100</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2523,34 +2784,40 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>400</v>
+      </c>
+      <c r="F58" s="3">
         <v>1500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H58" s="3">
         <v>2700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="I58" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J58" s="3">
         <v>1200</v>
       </c>
-      <c r="G58" s="3">
-        <v>1300</v>
-      </c>
-      <c r="H58" s="3">
-        <v>7600</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
@@ -2564,40 +2831,46 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2700</v>
+        <v>1200</v>
       </c>
       <c r="E59" s="3">
         <v>1200</v>
       </c>
       <c r="F59" s="3">
-        <v>1100</v>
+        <v>1400</v>
       </c>
       <c r="G59" s="3">
-        <v>500</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>1400</v>
+      </c>
+      <c r="H59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J59" s="3">
+        <v>400</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
-      </c>
-      <c r="M59" s="3">
-        <v>0</v>
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N59" s="3">
         <v>0</v>
@@ -2605,35 +2878,41 @@
       <c r="O59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F60" s="3">
         <v>10200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
+        <v>10200</v>
+      </c>
+      <c r="H60" s="3">
         <v>12400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="I60" s="3">
+        <v>12400</v>
+      </c>
+      <c r="J60" s="3">
         <v>9300</v>
       </c>
-      <c r="G60" s="3">
-        <v>6300</v>
-      </c>
-      <c r="H60" s="3">
-        <v>8300</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>100</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2646,32 +2925,38 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>2500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I61" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J61" s="3">
         <v>2700</v>
       </c>
-      <c r="G61" s="3">
-        <v>2600</v>
-      </c>
-      <c r="H61" s="3">
-        <v>2000</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2687,31 +2972,37 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -2728,8 +3019,14 @@
       <c r="O62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2769,8 +3066,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2810,8 +3113,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2851,35 +3160,41 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F66" s="3">
         <v>12700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
+        <v>12700</v>
+      </c>
+      <c r="H66" s="3">
         <v>14900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="I66" s="3">
+        <v>14900</v>
+      </c>
+      <c r="J66" s="3">
         <v>12100</v>
       </c>
-      <c r="G66" s="3">
-        <v>8800</v>
-      </c>
-      <c r="H66" s="3">
-        <v>10200</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>100</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2892,8 +3207,14 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2909,8 +3230,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2950,8 +3273,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2991,8 +3320,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3032,8 +3367,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3073,35 +3414,41 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-56000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-56000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-53400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
+        <v>-53400</v>
+      </c>
+      <c r="H72" s="3">
         <v>-27000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="I72" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="J72" s="3">
         <v>-21100</v>
       </c>
-      <c r="G72" s="3">
-        <v>-12000</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-13300</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-100</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3114,8 +3461,14 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3155,8 +3508,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3196,8 +3555,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3237,35 +3602,41 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F76" s="3">
         <v>-3800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="H76" s="3">
         <v>21600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
+        <v>21600</v>
+      </c>
+      <c r="J76" s="3">
         <v>26900</v>
       </c>
-      <c r="G76" s="3">
-        <v>34600</v>
-      </c>
-      <c r="H76" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>200</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3278,8 +3649,14 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3319,40 +3696,46 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44469</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3365,35 +3748,41 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-32300</v>
+        <v>-1300</v>
       </c>
       <c r="E81" s="3">
-        <v>-5900</v>
+        <v>-1300</v>
       </c>
       <c r="F81" s="3">
-        <v>-11700</v>
+        <v>-13200</v>
       </c>
       <c r="G81" s="3">
-        <v>-2600</v>
+        <v>-13200</v>
       </c>
       <c r="H81" s="3">
-        <v>-8000</v>
+        <v>-2900</v>
       </c>
       <c r="I81" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="K81" s="3">
         <v>-100</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3406,8 +3795,14 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3423,28 +3818,30 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>4300</v>
+        <v>1100</v>
       </c>
       <c r="E83" s="3">
-        <v>2200</v>
+        <v>1100</v>
       </c>
       <c r="F83" s="3">
-        <v>3800</v>
+        <v>1000</v>
       </c>
       <c r="G83" s="3">
-        <v>1700</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
+        <v>1000</v>
+      </c>
+      <c r="H83" s="3">
+        <v>100</v>
+      </c>
+      <c r="I83" s="3">
+        <v>100</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
@@ -3452,11 +3849,11 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -3464,8 +3861,14 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3505,8 +3908,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3546,8 +3955,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3587,8 +4002,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3628,8 +4049,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3669,34 +4096,40 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-1500</v>
+        <v>-1300</v>
       </c>
       <c r="E89" s="3">
-        <v>-900</v>
+        <v>-1300</v>
       </c>
       <c r="F89" s="3">
-        <v>-11500</v>
+        <v>-300</v>
       </c>
       <c r="G89" s="3">
-        <v>-8400</v>
+        <v>-300</v>
       </c>
       <c r="H89" s="3">
-        <v>-6500</v>
+        <v>-500</v>
       </c>
       <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
+        <v>-500</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="K89" s="3">
+        <v>0</v>
       </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
@@ -3710,8 +4143,14 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3727,22 +4166,24 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
       <c r="G91" s="3">
-        <v>-1100</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -3768,8 +4209,14 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3809,8 +4256,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3850,40 +4303,46 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F94" s="3">
-        <v>-4200</v>
+        <v>0</v>
       </c>
       <c r="G94" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -3891,8 +4350,14 @@
       <c r="O94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3908,31 +4373,33 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3949,8 +4416,14 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3990,8 +4463,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4031,8 +4510,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4072,35 +4557,41 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1500</v>
+        <v>4300</v>
       </c>
       <c r="E100" s="3">
-        <v>1200</v>
+        <v>4300</v>
       </c>
       <c r="F100" s="3">
-        <v>14100</v>
+        <v>100</v>
       </c>
       <c r="G100" s="3">
-        <v>14600</v>
+        <v>100</v>
       </c>
       <c r="H100" s="3">
-        <v>11000</v>
+        <v>600</v>
       </c>
       <c r="I100" s="3">
+        <v>600</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4113,34 +4604,40 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
         <v>-100</v>
       </c>
       <c r="F101" s="3">
-        <v>-1700</v>
+        <v>-300</v>
       </c>
       <c r="G101" s="3">
-        <v>-1100</v>
+        <v>-300</v>
       </c>
       <c r="H101" s="3">
         <v>-600</v>
       </c>
       <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
+        <v>-600</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
@@ -4154,35 +4651,41 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-200</v>
       </c>
-      <c r="E102" s="3">
-        <v>200</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-3200</v>
-      </c>
       <c r="G102" s="3">
-        <v>900</v>
+        <v>-200</v>
       </c>
       <c r="H102" s="3">
-        <v>3200</v>
+        <v>100</v>
       </c>
       <c r="I102" s="3">
+        <v>100</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="K102" s="3">
         <v>300</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4193,6 +4696,12 @@
         <v>3</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AKAN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AKAN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="92">
   <si>
     <t>AKAN</t>
   </si>
@@ -656,66 +656,67 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -728,8 +729,14 @@
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -740,10 +747,10 @@
         <v>200</v>
       </c>
       <c r="F8" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G8" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H8" s="3">
         <v>100</v>
@@ -752,22 +759,22 @@
         <v>100</v>
       </c>
       <c r="J8" s="3">
+        <v>100</v>
+      </c>
+      <c r="K8" s="3">
+        <v>100</v>
+      </c>
+      <c r="L8" s="3">
         <v>1300</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
@@ -775,8 +782,14 @@
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -787,10 +800,10 @@
         <v>200</v>
       </c>
       <c r="F9" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="G9" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="H9" s="3">
         <v>100</v>
@@ -799,14 +812,14 @@
         <v>100</v>
       </c>
       <c r="J9" s="3">
+        <v>100</v>
+      </c>
+      <c r="K9" s="3">
+        <v>100</v>
+      </c>
+      <c r="L9" s="3">
         <v>-300</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -822,23 +835,29 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
         <v>100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>100</v>
       </c>
-      <c r="F10" s="3">
-        <v>-400</v>
-      </c>
-      <c r="G10" s="3">
-        <v>-400</v>
-      </c>
       <c r="H10" s="3">
         <v>0</v>
       </c>
@@ -846,14 +865,14 @@
         <v>0</v>
       </c>
       <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
         <v>1600</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -869,8 +888,14 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -888,8 +913,10 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -935,8 +962,14 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,23 +1015,29 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F14" s="3">
         <v>-100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>-100</v>
       </c>
-      <c r="F14" s="3">
-        <v>11200</v>
-      </c>
-      <c r="G14" s="3">
-        <v>11200</v>
-      </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
@@ -1006,14 +1045,14 @@
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-100</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1029,22 +1068,28 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
         <v>100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>100</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1100</v>
       </c>
       <c r="H15" s="3">
         <v>100</v>
@@ -1053,14 +1098,14 @@
         <v>100</v>
       </c>
       <c r="J15" s="3">
+        <v>100</v>
+      </c>
+      <c r="K15" s="3">
+        <v>100</v>
+      </c>
+      <c r="L15" s="3">
         <v>1000</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1076,8 +1121,14 @@
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1092,41 +1143,43 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F17" s="3">
         <v>1400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1400</v>
       </c>
-      <c r="F17" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G17" s="3">
-        <v>2400</v>
-      </c>
       <c r="H17" s="3">
+        <v>600</v>
+      </c>
+      <c r="I17" s="3">
+        <v>600</v>
+      </c>
+      <c r="J17" s="3">
         <v>1400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>6000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>100</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1139,38 +1192,44 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1200</v>
       </c>
-      <c r="F18" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-2000</v>
-      </c>
       <c r="H18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J18" s="3">
         <v>-1300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-4800</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1186,8 +1245,14 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1205,8 +1270,10 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1231,11 +1298,11 @@
       <c r="J20" s="3">
         <v>0</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
@@ -1252,38 +1319,44 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-1100</v>
       </c>
-      <c r="F21" s="3">
-        <v>-900</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-900</v>
-      </c>
       <c r="H21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J21" s="3">
         <v>-1300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-1300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-3700</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1299,8 +1372,14 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1346,41 +1425,47 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1100</v>
       </c>
-      <c r="F23" s="3">
-        <v>-13200</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-13200</v>
-      </c>
       <c r="H23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J23" s="3">
         <v>-1300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-4700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-100</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1393,8 +1478,14 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1419,11 +1510,11 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1440,8 +1531,14 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1487,41 +1584,47 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1100</v>
       </c>
-      <c r="F26" s="3">
-        <v>-13200</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-13200</v>
-      </c>
       <c r="H26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J26" s="3">
         <v>-1300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-4700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-100</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1534,41 +1637,47 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-13200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-13200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-2900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-2900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-4500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-100</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1581,8 +1690,14 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1628,8 +1743,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1640,34 +1761,34 @@
         <v>-200</v>
       </c>
       <c r="F29" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="G29" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="H29" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="I29" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="J29" s="3">
         <v>-1600</v>
       </c>
-      <c r="I29" s="3">
+      <c r="K29" s="3">
         <v>-1600</v>
       </c>
-      <c r="J29" s="3">
+      <c r="L29" s="3">
         <v>200</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -1675,8 +1796,14 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1722,8 +1849,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1769,8 +1902,14 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1795,11 +1934,11 @@
       <c r="J32" s="3">
         <v>0</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
@@ -1816,41 +1955,47 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-13200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-13200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-2900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-2900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-4500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-100</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1863,8 +2008,14 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1910,41 +2061,47 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-13200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-13200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-2900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-2900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-4500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-100</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1957,46 +2114,52 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2009,8 +2172,14 @@
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2028,8 +2197,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2047,46 +2218,48 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F41" s="3">
         <v>6000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>6000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>200</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N41" s="3">
-        <v>0</v>
-      </c>
-      <c r="O41" s="3">
-        <v>0</v>
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P41" s="3">
         <v>0</v>
@@ -2094,8 +2267,14 @@
       <c r="Q41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3">
+        <v>0</v>
+      </c>
+      <c r="S41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2112,28 +2291,28 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
         <v>300</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
+      <c r="K42" s="3">
+        <v>300</v>
+      </c>
+      <c r="L42" s="3">
+        <v>300</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -2141,16 +2320,22 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="E43" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="F43" s="3">
         <v>300</v>
@@ -2159,28 +2344,28 @@
         <v>300</v>
       </c>
       <c r="H43" s="3">
+        <v>300</v>
+      </c>
+      <c r="I43" s="3">
+        <v>300</v>
+      </c>
+      <c r="J43" s="3">
         <v>700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1200</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
-      </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -2188,8 +2373,14 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2199,11 +2390,11 @@
       <c r="E44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F44" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G44" s="3">
-        <v>1300</v>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H44" s="3">
         <v>1300</v>
@@ -2212,22 +2403,22 @@
         <v>1300</v>
       </c>
       <c r="J44" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K44" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L44" s="3">
         <v>1100</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
-      </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2235,8 +2426,14 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2252,23 +2449,23 @@
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>300</v>
-      </c>
-      <c r="I45" s="3">
-        <v>300</v>
-      </c>
-      <c r="J45" s="3">
-        <v>800</v>
       </c>
       <c r="K45" s="3">
         <v>300</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
+      <c r="L45" s="3">
+        <v>800</v>
+      </c>
+      <c r="M45" s="3">
+        <v>300</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
@@ -2282,41 +2479,47 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F46" s="3">
         <v>7600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>7600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>3200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>3800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>300</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2329,8 +2532,14 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2364,11 +2573,11 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
-      </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -2376,38 +2585,44 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F48" s="3">
         <v>1700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>11800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>11800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>12500</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2423,8 +2638,14 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2435,26 +2656,26 @@
         <v>0</v>
       </c>
       <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>3800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>3800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>21000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>21000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>22200</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2470,8 +2691,14 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2517,8 +2744,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2564,8 +2797,14 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2590,11 +2829,11 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -2611,8 +2850,14 @@
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2658,41 +2903,47 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F54" s="3">
         <v>10000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>10000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>8800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>8800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>36500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>36500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>39000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>300</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2705,8 +2956,14 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2724,8 +2981,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2743,41 +3002,43 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F57" s="3">
         <v>3600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>3600</v>
       </c>
-      <c r="F57" s="3">
-        <v>6000</v>
-      </c>
-      <c r="G57" s="3">
-        <v>6000</v>
-      </c>
       <c r="H57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="I57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="J57" s="3">
         <v>8500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>8500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>7100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>100</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2790,8 +3051,14 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2802,28 +3069,28 @@
         <v>400</v>
       </c>
       <c r="F58" s="3">
+        <v>400</v>
+      </c>
+      <c r="G58" s="3">
+        <v>400</v>
+      </c>
+      <c r="H58" s="3">
         <v>1500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1200</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
+      <c r="M58" s="3">
+        <v>0</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
@@ -2837,46 +3104,52 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>300</v>
+      </c>
+      <c r="F59" s="3">
         <v>1200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1200</v>
       </c>
-      <c r="F59" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1400</v>
-      </c>
       <c r="H59" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I59" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J59" s="3">
         <v>1200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>400</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N59" s="3">
-        <v>0</v>
-      </c>
-      <c r="O59" s="3">
-        <v>0</v>
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P59" s="3">
         <v>0</v>
@@ -2884,41 +3157,47 @@
       <c r="Q59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3">
+        <v>0</v>
+      </c>
+      <c r="S59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F60" s="3">
         <v>5400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>5400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>10200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>10200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>12400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>12400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>9300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>100</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2931,8 +3210,14 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2943,10 +3228,10 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>2500</v>
@@ -2955,14 +3240,14 @@
         <v>2500</v>
       </c>
       <c r="J61" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K61" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L61" s="3">
         <v>2700</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2978,8 +3263,14 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3004,11 +3295,11 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -3025,8 +3316,14 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3072,8 +3369,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3119,8 +3422,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3166,41 +3475,47 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F66" s="3">
         <v>5400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>5400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>12700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>12700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>14900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>14900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>12100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>100</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3213,8 +3528,14 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3232,8 +3553,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3279,8 +3602,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3326,8 +3655,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3373,8 +3708,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3420,41 +3761,47 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-57500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-57500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-56000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-56000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-53400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-53400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-27000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-27000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-21100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-100</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3467,8 +3814,14 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3514,8 +3867,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3561,8 +3920,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3608,41 +3973,47 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F76" s="3">
         <v>4600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-3800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-3800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>21600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>21600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>26900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>200</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3655,8 +4026,14 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3702,46 +4079,52 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3754,41 +4137,47 @@
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-13200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-13200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-2900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-2900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-4500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-100</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3801,8 +4190,14 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3820,8 +4215,10 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3832,34 +4229,34 @@
         <v>1100</v>
       </c>
       <c r="F83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H83" s="3">
         <v>1000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>1000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>100</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
-      <c r="O83" s="3">
-        <v>0</v>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
@@ -3867,8 +4264,14 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3914,8 +4317,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3961,8 +4370,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4008,8 +4423,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4055,8 +4476,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4102,40 +4529,46 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1600</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
+      <c r="M89" s="3">
+        <v>0</v>
       </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
@@ -4149,8 +4582,14 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4168,23 +4607,25 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F91" s="3">
         <v>-700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-700</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
@@ -4215,8 +4656,14 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4262,8 +4709,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4309,23 +4762,29 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F94" s="3">
         <v>100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
@@ -4335,20 +4794,20 @@
       <c r="J94" s="3">
         <v>0</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
@@ -4356,8 +4815,14 @@
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4375,8 +4840,10 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4401,11 +4868,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4422,8 +4889,14 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4469,8 +4942,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4516,8 +4995,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4563,41 +5048,47 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>200</v>
+      </c>
+      <c r="F100" s="3">
         <v>4300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>4300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>300</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4610,40 +5101,46 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-600</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
@@ -4657,41 +5154,47 @@
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F102" s="3">
         <v>3000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>3000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-2100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>300</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4702,6 +5205,12 @@
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AKAN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AKAN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="92">
   <si>
     <t>AKAN</t>
   </si>
@@ -4240,8 +4240,8 @@
       <c r="I83" s="3">
         <v>1000</v>
       </c>
-      <c r="J83" s="3">
-        <v>100</v>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3">
         <v>100</v>
@@ -5130,8 +5130,8 @@
       <c r="I101" s="3">
         <v>-300</v>
       </c>
-      <c r="J101" s="3">
-        <v>-600</v>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>-600</v>
